--- a/unit2_file/unit2_file.xlsx
+++ b/unit2_file/unit2_file.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE09B58-BD63-4EC1-8D34-9AD3B4986001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43A36BAA-7A4E-416D-8974-35C772B58878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Muc luc" sheetId="9" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="430">
   <si>
     <t>1. Trong Linux, mọi thứ đều là file</t>
   </si>
@@ -3257,864 +3257,16 @@
     <t>5. Các hàm thao tác với chuỗi trong file.</t>
   </si>
   <si>
-    <t>* Nói về hàm perror và biến toàn cục errno:</t>
-  </si>
-  <si>
-    <r>
-      <t>1. errno</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>errno</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> là một biến toàn cục trong thư viện C của hệ thống Unix/Linux, chứa mã lỗi của các cuộc gọi hệ thống hoặc các hàm thư viện C.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Khi một hàm gặp lỗi (thường là một cuộc gọi hệ thống như </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>open()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>read()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>write()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, v.v.), nó sẽ không trả về giá trị cụ thể để chỉ ra lỗi. Thay vào đó, hệ thống sẽ thiết lập giá trị cho </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>errno</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> để chỉ ra loại lỗi đã xảy ra.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Sau khi một hàm gặp lỗi, bạn có thể kiểm tra giá trị của </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>errno</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> để biết chính xác lỗi là gì.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Các mã lỗi trong </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>errno</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> là các hằng số được định nghĩa trong header file </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>&lt;errno.h&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, ví dụ như </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>EIO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (Input/Output error), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>ENOMEM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (Out of memory), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>EBADF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (Bad file descriptor), v.v.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>2. perror</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>perror</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> là một hàm thư viện C được sử dụng để in thông báo lỗi liên quan đến </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>errno</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ra màn hình. Hàm này sẽ kết hợp một chuỗi mô tả tùy chọn với thông điệp lỗi tương ứng với giá trị của </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>errno</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> và in chúng ra </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>stderr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>perror</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> thường được sử dụng sau khi một cuộc gọi hệ thống trả về lỗi để người lập trình biết được lý do lỗi.</t>
-    </r>
-  </si>
-  <si>
-    <t>Cú pháp:</t>
-  </si>
-  <si>
-    <t>void perror(const char *s);</t>
-  </si>
-  <si>
-    <r>
-      <t>s</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> là chuỗi mô tả bạn muốn thêm vào thông báo lỗi (thường là tên của hàm hoặc tên của một hoạt động mà bạn đang thực hiện).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Hàm này sẽ in ra thông báo lỗi, bao gồm cả chuỗi </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>s</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (nếu có) và thông báo lỗi được dịch từ mã </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>errno</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Giả sử bạn đang cố mở một file và hàm </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>open()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> gặp lỗi, sau đó bạn muốn in thông báo lỗi chi tiết.</t>
-    </r>
-  </si>
-  <si>
     <t>#include &lt;stdio.h&gt;</t>
   </si>
   <si>
-    <t>#include &lt;fcntl.h&gt;   // Để sử dụng open()</t>
-  </si>
-  <si>
-    <t>#include &lt;unistd.h&gt;  // Để sử dụng close()</t>
-  </si>
-  <si>
-    <t>#include &lt;errno.h&gt;   // Để sử dụng errno</t>
-  </si>
-  <si>
-    <t>#include &lt;string.h&gt;  // Để sử dụng strerror()</t>
-  </si>
-  <si>
     <t>int main() {</t>
   </si>
   <si>
-    <t xml:space="preserve">    // Cố mở một file không tồn tại</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    int fd = open("nonexistent_file.txt", O_RDONLY);</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">    // Kiểm tra xem open có gặp lỗi không</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    if (fd == -1) {</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        // Sử dụng perror để in thông báo lỗi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        perror("Error opening file");</t>
-  </si>
-  <si>
     <t xml:space="preserve">    }</t>
   </si>
   <si>
     <t xml:space="preserve">    return 0;</t>
-  </si>
-  <si>
-    <r>
-      <t>1. open("nonexistent_file.txt", O_RDONLY)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Hàm </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>open</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> sẽ cố mở file "nonexistent_file.txt" với chế độ chỉ đọc (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>O_RDONLY</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Vì file không tồn tại, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>open</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> sẽ trả về </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> và thiết lập giá trị cho biến toàn cục </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>errno</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>2. perror("Error opening file")</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Sau khi phát hiện lỗi (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>fd == -1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">), chúng ta gọi </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>perror</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>perror</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> sẽ in ra chuỗi </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>"Error opening file"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> và thông báo lỗi tương ứng với giá trị của </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>errno</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, ví dụ như:</t>
-    </r>
-  </si>
-  <si>
-    <t>Error opening file: No such file or directory</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Thông báo này cho biết rằng lỗi là do file không tồn tại (lỗi </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>ENOENT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Các mã lỗi phổ biến trong </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>errno</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="13.5"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ENOENT</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (2)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: No such file or directory.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>EACCES</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (13)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Permission denied.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ENOMEM</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (12)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Out of memory.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>EIO</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (5)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Input/output error.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>EBADF</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (9)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Bad file descriptor.</t>
-    </r>
   </si>
   <si>
     <t>Hàm thao tác với file thư viện C</t>
@@ -7309,7 +6461,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -7349,20 +6501,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
@@ -7394,14 +6533,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7412,8 +6553,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -7836,92 +6975,9 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>414619</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>112059</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="7668695" cy="409632"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8949019" y="78426609"/>
-          <a:ext cx="7668695" cy="409632"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>392206</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>67236</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="7278116" cy="6820852"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8926606" y="78953286"/>
-          <a:ext cx="7278116" cy="6820852"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>336176</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>12847</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="8391095" cy="4703289"/>
@@ -7958,10 +7014,10 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>392206</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>33616</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>415066</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>25996</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4426644" cy="3559808"/>
     <xdr:pic>
@@ -7985,7 +7041,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18042031" y="94921666"/>
+          <a:off x="17849626" y="10297756"/>
           <a:ext cx="4426644" cy="3559808"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7998,7 +7054,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -8347,42 +7403,42 @@
   <dimension ref="B2:B14"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="16384" width="8.796875" style="45"/>
+    <col min="1" max="16384" width="8.796875" style="34"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:2">
-      <c r="B2" s="44" t="s">
-        <v>462</v>
+      <c r="B2" s="33" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="4" spans="2:2">
-      <c r="B4" s="44" t="s">
-        <v>463</v>
+      <c r="B4" s="33" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="2:2">
-      <c r="B6" s="44" t="s">
-        <v>464</v>
+      <c r="B6" s="33" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="8" spans="2:2">
-      <c r="B8" s="44" t="s">
-        <v>465</v>
+      <c r="B8" s="33" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="10" spans="2:2">
-      <c r="B10" s="44" t="s">
-        <v>466</v>
+      <c r="B10" s="33" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="12" spans="2:2">
-      <c r="B12" s="44" t="s">
-        <v>467</v>
+      <c r="B12" s="33" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="14" spans="2:2">
-      <c r="B14" s="44" t="s">
-        <v>468</v>
+      <c r="B14" s="33" t="s">
+        <v>429</v>
       </c>
     </row>
   </sheetData>
@@ -9786,1227 +8842,990 @@
       <c r="B1" s="4"/>
     </row>
     <row r="2" spans="1:27">
-      <c r="A2" s="29"/>
-      <c r="B2" s="30" t="s">
-        <v>245</v>
-      </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="30" t="s">
-        <v>246</v>
-      </c>
-      <c r="O2" s="31"/>
-      <c r="P2" s="31"/>
-      <c r="Q2" s="31"/>
-      <c r="R2" s="31"/>
-      <c r="S2" s="31"/>
-      <c r="T2" s="31"/>
-      <c r="U2" s="31"/>
-      <c r="V2" s="31"/>
-      <c r="W2" s="31"/>
-      <c r="X2" s="31"/>
-      <c r="Y2" s="31"/>
-      <c r="Z2" s="31"/>
-      <c r="AA2" s="32"/>
+      <c r="A2" s="24"/>
+      <c r="B2" s="25" t="s">
+        <v>206</v>
+      </c>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="26"/>
+      <c r="Y2" s="26"/>
+      <c r="Z2" s="26"/>
+      <c r="AA2" s="27"/>
     </row>
     <row r="3" spans="1:27" ht="22.8">
-      <c r="A3" s="33"/>
+      <c r="A3" s="28"/>
       <c r="B3" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="L3" s="34"/>
-      <c r="M3" s="33"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="28"/>
       <c r="N3" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="AA3" s="34"/>
+        <v>208</v>
+      </c>
+      <c r="AA3" s="29"/>
     </row>
     <row r="4" spans="1:27">
-      <c r="A4" s="33"/>
-      <c r="L4" s="34"/>
-      <c r="M4" s="33"/>
-      <c r="AA4" s="34"/>
+      <c r="A4" s="28"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="28"/>
+      <c r="AA4" s="29"/>
     </row>
     <row r="5" spans="1:27" ht="17.399999999999999">
-      <c r="A5" s="33"/>
+      <c r="A5" s="28"/>
       <c r="B5" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="L5" s="34"/>
-      <c r="M5" s="33"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="28"/>
       <c r="N5" s="13" t="s">
-        <v>248</v>
+        <v>209</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="AA5" s="34"/>
+        <v>210</v>
+      </c>
+      <c r="AA5" s="29"/>
     </row>
     <row r="6" spans="1:27" ht="17.399999999999999">
-      <c r="A6" s="33"/>
+      <c r="A6" s="28"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="L6" s="34"/>
-      <c r="M6" s="33"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="28"/>
       <c r="N6" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="AA6" s="34"/>
+        <v>211</v>
+      </c>
+      <c r="AA6" s="29"/>
     </row>
     <row r="7" spans="1:27">
-      <c r="A7" s="33"/>
+      <c r="A7" s="28"/>
       <c r="C7" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="L7" s="34"/>
-      <c r="M7" s="33"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="28"/>
       <c r="N7" s="1"/>
       <c r="O7" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="AA7" s="34"/>
+        <v>212</v>
+      </c>
+      <c r="AA7" s="29"/>
     </row>
     <row r="8" spans="1:27">
-      <c r="A8" s="33"/>
+      <c r="A8" s="28"/>
       <c r="C8" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="L8" s="34"/>
-      <c r="M8" s="33"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="28"/>
       <c r="O8" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="AA8" s="34"/>
+        <v>213</v>
+      </c>
+      <c r="AA8" s="29"/>
     </row>
     <row r="9" spans="1:27">
-      <c r="A9" s="33"/>
+      <c r="A9" s="28"/>
       <c r="C9" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="L9" s="34"/>
-      <c r="M9" s="33"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="28"/>
       <c r="N9" s="1"/>
       <c r="O9" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="AA9" s="34"/>
+        <v>214</v>
+      </c>
+      <c r="AA9" s="29"/>
     </row>
     <row r="10" spans="1:27" ht="17.399999999999999">
-      <c r="A10" s="33"/>
+      <c r="A10" s="28"/>
       <c r="C10" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="L10" s="34"/>
-      <c r="M10" s="33"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="28"/>
       <c r="N10" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="AA10" s="34"/>
+        <v>215</v>
+      </c>
+      <c r="AA10" s="29"/>
     </row>
     <row r="11" spans="1:27">
-      <c r="A11" s="33"/>
+      <c r="A11" s="28"/>
       <c r="C11" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="L11" s="34"/>
-      <c r="M11" s="33"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="28"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="AA11" s="34"/>
+        <v>216</v>
+      </c>
+      <c r="AA11" s="29"/>
     </row>
     <row r="12" spans="1:27">
-      <c r="A12" s="33"/>
+      <c r="A12" s="28"/>
       <c r="D12" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="L12" s="34"/>
-      <c r="M12" s="33"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="28"/>
       <c r="O12" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA12" s="34"/>
+        <v>217</v>
+      </c>
+      <c r="AA12" s="29"/>
     </row>
     <row r="13" spans="1:27">
-      <c r="A13" s="33"/>
+      <c r="A13" s="28"/>
       <c r="D13" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="L13" s="34"/>
-      <c r="M13" s="33"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="28"/>
       <c r="O13" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="AA13" s="34"/>
+        <v>218</v>
+      </c>
+      <c r="AA13" s="29"/>
     </row>
     <row r="14" spans="1:27" ht="17.399999999999999">
-      <c r="A14" s="33"/>
+      <c r="A14" s="28"/>
       <c r="D14" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="L14" s="34"/>
-      <c r="M14" s="33"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="28"/>
       <c r="N14" s="13" t="s">
-        <v>258</v>
+        <v>219</v>
       </c>
       <c r="O14" s="1"/>
-      <c r="AA14" s="34"/>
+      <c r="AA14" s="29"/>
     </row>
     <row r="15" spans="1:27">
-      <c r="A15" s="33"/>
+      <c r="A15" s="28"/>
       <c r="D15" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="L15" s="34"/>
-      <c r="M15" s="33"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="28"/>
       <c r="O15" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="AA15" s="34"/>
+        <v>220</v>
+      </c>
+      <c r="AA15" s="29"/>
     </row>
     <row r="16" spans="1:27">
-      <c r="A16" s="33"/>
+      <c r="A16" s="28"/>
       <c r="C16" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="L16" s="34"/>
-      <c r="M16" s="33"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="28"/>
       <c r="O16" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="AA16" s="34"/>
+        <v>221</v>
+      </c>
+      <c r="AA16" s="29"/>
     </row>
     <row r="17" spans="1:27">
-      <c r="A17" s="33"/>
-      <c r="L17" s="34"/>
-      <c r="M17" s="33"/>
+      <c r="A17" s="28"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="28"/>
       <c r="O17" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="AA17" s="34"/>
+        <v>222</v>
+      </c>
+      <c r="AA17" s="29"/>
     </row>
     <row r="18" spans="1:27" ht="17.399999999999999">
-      <c r="A18" s="33"/>
+      <c r="A18" s="28"/>
       <c r="B18" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="L18" s="34"/>
-      <c r="M18" s="33"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="28"/>
       <c r="O18" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="AA18" s="34"/>
+        <v>223</v>
+      </c>
+      <c r="AA18" s="29"/>
     </row>
     <row r="19" spans="1:27">
-      <c r="A19" s="33"/>
+      <c r="A19" s="28"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="L19" s="34"/>
-      <c r="M19" s="33"/>
+      <c r="L19" s="29"/>
+      <c r="M19" s="28"/>
       <c r="N19" s="12"/>
       <c r="O19" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="AA19" s="34"/>
+        <v>224</v>
+      </c>
+      <c r="AA19" s="29"/>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="33"/>
+      <c r="A20" s="28"/>
       <c r="C20" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="L20" s="34"/>
-      <c r="M20" s="33"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="28"/>
       <c r="N20" s="14"/>
       <c r="O20" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="AA20" s="34"/>
+      <c r="AA20" s="29"/>
     </row>
     <row r="21" spans="1:27">
-      <c r="A21" s="33"/>
+      <c r="A21" s="28"/>
       <c r="D21" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="L21" s="34"/>
-      <c r="M21" s="33"/>
+      <c r="L21" s="29"/>
+      <c r="M21" s="28"/>
       <c r="N21" s="14"/>
       <c r="O21" s="12"/>
-      <c r="AA21" s="34"/>
+      <c r="AA21" s="29"/>
     </row>
     <row r="22" spans="1:27">
-      <c r="A22" s="33"/>
+      <c r="A22" s="28"/>
       <c r="D22" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="L22" s="34"/>
-      <c r="M22" s="33"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="28"/>
       <c r="O22" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="AA22" s="34"/>
+        <v>225</v>
+      </c>
+      <c r="AA22" s="29"/>
     </row>
     <row r="23" spans="1:27">
-      <c r="A23" s="33"/>
+      <c r="A23" s="28"/>
       <c r="D23" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="L23" s="34"/>
-      <c r="M23" s="33"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="28"/>
       <c r="O23" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="AA23" s="34"/>
+        <v>226</v>
+      </c>
+      <c r="AA23" s="29"/>
     </row>
     <row r="24" spans="1:27">
-      <c r="A24" s="33"/>
+      <c r="A24" s="28"/>
       <c r="D24" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="L24" s="34"/>
-      <c r="M24" s="33"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="28"/>
       <c r="O24" s="14" t="s">
-        <v>266</v>
-      </c>
-      <c r="AA24" s="34"/>
+        <v>227</v>
+      </c>
+      <c r="AA24" s="29"/>
     </row>
     <row r="25" spans="1:27">
-      <c r="A25" s="33"/>
+      <c r="A25" s="28"/>
       <c r="C25" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="L25" s="34"/>
-      <c r="M25" s="33"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="28"/>
       <c r="O25" s="14" t="s">
-        <v>267</v>
-      </c>
-      <c r="AA25" s="34"/>
+        <v>228</v>
+      </c>
+      <c r="AA25" s="29"/>
     </row>
     <row r="26" spans="1:27">
-      <c r="A26" s="33"/>
-      <c r="L26" s="34"/>
-      <c r="M26" s="33"/>
+      <c r="A26" s="28"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="28"/>
       <c r="O26" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="AA26" s="34"/>
+        <v>229</v>
+      </c>
+      <c r="AA26" s="29"/>
     </row>
     <row r="27" spans="1:27" ht="17.399999999999999">
-      <c r="A27" s="33"/>
+      <c r="A27" s="28"/>
       <c r="B27" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="L27" s="34"/>
-      <c r="M27" s="33"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="28"/>
       <c r="O27" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="AA27" s="34"/>
+        <v>230</v>
+      </c>
+      <c r="AA27" s="29"/>
     </row>
     <row r="28" spans="1:27">
-      <c r="A28" s="33"/>
+      <c r="A28" s="28"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="L28" s="34"/>
-      <c r="M28" s="33"/>
+      <c r="L28" s="29"/>
+      <c r="M28" s="28"/>
       <c r="O28" s="14" t="s">
-        <v>270</v>
-      </c>
-      <c r="AA28" s="34"/>
+        <v>231</v>
+      </c>
+      <c r="AA28" s="29"/>
     </row>
     <row r="29" spans="1:27">
-      <c r="A29" s="33"/>
+      <c r="A29" s="28"/>
       <c r="D29" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="L29" s="34"/>
-      <c r="M29" s="33"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="28"/>
       <c r="O29" s="14" t="s">
-        <v>271</v>
-      </c>
-      <c r="AA29" s="34"/>
+        <v>232</v>
+      </c>
+      <c r="AA29" s="29"/>
     </row>
     <row r="30" spans="1:27">
-      <c r="A30" s="33"/>
+      <c r="A30" s="28"/>
       <c r="D30" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="L30" s="34"/>
-      <c r="M30" s="33"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="28"/>
       <c r="O30" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="AA30" s="34"/>
+      <c r="AA30" s="29"/>
     </row>
     <row r="31" spans="1:27">
-      <c r="A31" s="33"/>
+      <c r="A31" s="28"/>
       <c r="D31" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="L31" s="34"/>
-      <c r="M31" s="33"/>
+      <c r="L31" s="29"/>
+      <c r="M31" s="28"/>
       <c r="O31" s="12"/>
-      <c r="AA31" s="34"/>
+      <c r="AA31" s="29"/>
     </row>
     <row r="32" spans="1:27">
-      <c r="A32" s="33"/>
+      <c r="A32" s="28"/>
       <c r="C32" s="1"/>
-      <c r="L32" s="34"/>
-      <c r="M32" s="33"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="28"/>
       <c r="O32" s="14" t="s">
-        <v>272</v>
-      </c>
-      <c r="AA32" s="34"/>
+        <v>233</v>
+      </c>
+      <c r="AA32" s="29"/>
     </row>
     <row r="33" spans="1:27" ht="22.8">
-      <c r="A33" s="33"/>
+      <c r="A33" s="28"/>
       <c r="C33" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="L33" s="34"/>
-      <c r="M33" s="33"/>
+      <c r="L33" s="29"/>
+      <c r="M33" s="28"/>
       <c r="N33" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="AA33" s="34"/>
+        <v>234</v>
+      </c>
+      <c r="AA33" s="29"/>
     </row>
     <row r="34" spans="1:27" ht="17.399999999999999">
-      <c r="A34" s="33"/>
+      <c r="A34" s="28"/>
       <c r="B34" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="L34" s="34"/>
-      <c r="M34" s="33"/>
-      <c r="AA34" s="34"/>
+      <c r="L34" s="29"/>
+      <c r="M34" s="28"/>
+      <c r="AA34" s="29"/>
     </row>
     <row r="35" spans="1:27" ht="17.399999999999999">
-      <c r="A35" s="33"/>
+      <c r="A35" s="28"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="L35" s="34"/>
-      <c r="M35" s="33"/>
+      <c r="L35" s="29"/>
+      <c r="M35" s="28"/>
       <c r="N35" s="13" t="s">
-        <v>248</v>
+        <v>209</v>
       </c>
       <c r="P35" s="14" t="s">
-        <v>274</v>
-      </c>
-      <c r="AA35" s="34"/>
+        <v>235</v>
+      </c>
+      <c r="AA35" s="29"/>
     </row>
     <row r="36" spans="1:27" ht="17.399999999999999">
-      <c r="A36" s="33"/>
+      <c r="A36" s="28"/>
       <c r="C36" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="L36" s="34"/>
-      <c r="M36" s="33"/>
+      <c r="L36" s="29"/>
+      <c r="M36" s="28"/>
       <c r="N36" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="AA36" s="34"/>
+        <v>211</v>
+      </c>
+      <c r="AA36" s="29"/>
     </row>
     <row r="37" spans="1:27">
-      <c r="A37" s="33"/>
+      <c r="A37" s="28"/>
       <c r="D37" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="L37" s="34"/>
-      <c r="M37" s="33"/>
+      <c r="L37" s="29"/>
+      <c r="M37" s="28"/>
       <c r="N37" s="1"/>
       <c r="O37" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="AA37" s="34"/>
+        <v>236</v>
+      </c>
+      <c r="AA37" s="29"/>
     </row>
     <row r="38" spans="1:27">
-      <c r="A38" s="33"/>
+      <c r="A38" s="28"/>
       <c r="D38" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="L38" s="34"/>
-      <c r="M38" s="33"/>
+      <c r="L38" s="29"/>
+      <c r="M38" s="28"/>
       <c r="O38" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="AA38" s="34"/>
+        <v>237</v>
+      </c>
+      <c r="AA38" s="29"/>
     </row>
     <row r="39" spans="1:27">
-      <c r="A39" s="33"/>
+      <c r="A39" s="28"/>
       <c r="C39" s="1"/>
-      <c r="L39" s="34"/>
-      <c r="M39" s="33"/>
+      <c r="L39" s="29"/>
+      <c r="M39" s="28"/>
       <c r="N39" s="1"/>
       <c r="O39" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="AA39" s="34"/>
+        <v>238</v>
+      </c>
+      <c r="AA39" s="29"/>
     </row>
     <row r="40" spans="1:27" ht="17.399999999999999">
-      <c r="A40" s="33"/>
+      <c r="A40" s="28"/>
       <c r="C40" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="L40" s="34"/>
-      <c r="M40" s="33"/>
+      <c r="L40" s="29"/>
+      <c r="M40" s="28"/>
       <c r="N40" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="AA40" s="34"/>
+        <v>215</v>
+      </c>
+      <c r="AA40" s="29"/>
     </row>
     <row r="41" spans="1:27">
-      <c r="A41" s="33"/>
-      <c r="L41" s="34"/>
-      <c r="M41" s="33"/>
+      <c r="A41" s="28"/>
+      <c r="L41" s="29"/>
+      <c r="M41" s="28"/>
       <c r="N41" s="1"/>
       <c r="O41" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="AA41" s="34"/>
+        <v>239</v>
+      </c>
+      <c r="AA41" s="29"/>
     </row>
     <row r="42" spans="1:27" ht="22.8">
-      <c r="A42" s="33"/>
+      <c r="A42" s="28"/>
       <c r="B42" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="L42" s="34"/>
-      <c r="M42" s="33"/>
+      <c r="L42" s="29"/>
+      <c r="M42" s="28"/>
       <c r="O42" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="AA42" s="34"/>
+        <v>240</v>
+      </c>
+      <c r="AA42" s="29"/>
     </row>
     <row r="43" spans="1:27">
-      <c r="A43" s="33"/>
-      <c r="L43" s="34"/>
-      <c r="M43" s="33"/>
+      <c r="A43" s="28"/>
+      <c r="L43" s="29"/>
+      <c r="M43" s="28"/>
       <c r="N43" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="AA43" s="34"/>
+        <v>241</v>
+      </c>
+      <c r="AA43" s="29"/>
     </row>
     <row r="44" spans="1:27" ht="17.399999999999999">
-      <c r="A44" s="33"/>
+      <c r="A44" s="28"/>
       <c r="B44" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="L44" s="34"/>
-      <c r="M44" s="33"/>
+      <c r="L44" s="29"/>
+      <c r="M44" s="28"/>
       <c r="N44" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="AA44" s="34"/>
+        <v>219</v>
+      </c>
+      <c r="AA44" s="29"/>
     </row>
     <row r="45" spans="1:27">
-      <c r="A45" s="33"/>
+      <c r="A45" s="28"/>
       <c r="C45" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="L45" s="34"/>
-      <c r="M45" s="33"/>
+      <c r="L45" s="29"/>
+      <c r="M45" s="28"/>
       <c r="N45" s="12"/>
       <c r="O45" s="14" t="s">
-        <v>281</v>
-      </c>
-      <c r="AA45" s="34"/>
+        <v>242</v>
+      </c>
+      <c r="AA45" s="29"/>
     </row>
     <row r="46" spans="1:27">
-      <c r="A46" s="33"/>
+      <c r="A46" s="28"/>
       <c r="C46" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="L46" s="34"/>
-      <c r="M46" s="33"/>
+      <c r="L46" s="29"/>
+      <c r="M46" s="28"/>
       <c r="N46" s="14"/>
       <c r="O46" s="14" t="s">
-        <v>282</v>
-      </c>
-      <c r="AA46" s="34"/>
+        <v>243</v>
+      </c>
+      <c r="AA46" s="29"/>
     </row>
     <row r="47" spans="1:27">
-      <c r="A47" s="33"/>
+      <c r="A47" s="28"/>
       <c r="D47" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="L47" s="34"/>
-      <c r="M47" s="33"/>
+      <c r="L47" s="29"/>
+      <c r="M47" s="28"/>
       <c r="N47" s="14"/>
       <c r="O47" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="AA47" s="34"/>
+        <v>222</v>
+      </c>
+      <c r="AA47" s="29"/>
     </row>
     <row r="48" spans="1:27" ht="17.399999999999999">
-      <c r="A48" s="33"/>
+      <c r="A48" s="28"/>
       <c r="B48" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="L48" s="34"/>
-      <c r="M48" s="33"/>
+      <c r="L48" s="29"/>
+      <c r="M48" s="28"/>
       <c r="O48" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="AA48" s="34"/>
+        <v>223</v>
+      </c>
+      <c r="AA48" s="29"/>
     </row>
     <row r="49" spans="1:27">
-      <c r="A49" s="33"/>
+      <c r="A49" s="28"/>
       <c r="C49" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="L49" s="34"/>
-      <c r="M49" s="33"/>
+      <c r="L49" s="29"/>
+      <c r="M49" s="28"/>
       <c r="O49" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="AA49" s="34"/>
+        <v>224</v>
+      </c>
+      <c r="AA49" s="29"/>
     </row>
     <row r="50" spans="1:27">
-      <c r="A50" s="33"/>
+      <c r="A50" s="28"/>
       <c r="C50" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="L50" s="34"/>
-      <c r="M50" s="33"/>
+      <c r="L50" s="29"/>
+      <c r="M50" s="28"/>
       <c r="O50" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="AA50" s="34"/>
+      <c r="AA50" s="29"/>
     </row>
     <row r="51" spans="1:27">
-      <c r="A51" s="33"/>
+      <c r="A51" s="28"/>
       <c r="D51" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="L51" s="34"/>
-      <c r="M51" s="33"/>
+      <c r="L51" s="29"/>
+      <c r="M51" s="28"/>
       <c r="O51" s="12"/>
-      <c r="AA51" s="34"/>
+      <c r="AA51" s="29"/>
     </row>
     <row r="52" spans="1:27" ht="17.399999999999999">
-      <c r="A52" s="33"/>
+      <c r="A52" s="28"/>
       <c r="B52" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="L52" s="34"/>
-      <c r="M52" s="33"/>
+      <c r="L52" s="29"/>
+      <c r="M52" s="28"/>
       <c r="O52" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="AA52" s="34"/>
+        <v>244</v>
+      </c>
+      <c r="AA52" s="29"/>
     </row>
     <row r="53" spans="1:27">
-      <c r="A53" s="33"/>
+      <c r="A53" s="28"/>
       <c r="C53" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="L53" s="34"/>
-      <c r="M53" s="33"/>
+      <c r="L53" s="29"/>
+      <c r="M53" s="28"/>
       <c r="O53" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="AA53" s="34"/>
+        <v>245</v>
+      </c>
+      <c r="AA53" s="29"/>
     </row>
     <row r="54" spans="1:27">
-      <c r="A54" s="33"/>
+      <c r="A54" s="28"/>
       <c r="D54" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="L54" s="34"/>
-      <c r="M54" s="33"/>
+      <c r="L54" s="29"/>
+      <c r="M54" s="28"/>
       <c r="O54" s="14" t="s">
-        <v>285</v>
-      </c>
-      <c r="AA54" s="34"/>
+        <v>246</v>
+      </c>
+      <c r="AA54" s="29"/>
     </row>
     <row r="55" spans="1:27" ht="17.399999999999999">
-      <c r="A55" s="33"/>
+      <c r="A55" s="28"/>
       <c r="B55" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="L55" s="34"/>
-      <c r="M55" s="33"/>
+      <c r="L55" s="29"/>
+      <c r="M55" s="28"/>
       <c r="O55" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="AA55" s="34"/>
+      <c r="AA55" s="29"/>
     </row>
     <row r="56" spans="1:27">
-      <c r="A56" s="33"/>
+      <c r="A56" s="28"/>
       <c r="C56" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="L56" s="34"/>
-      <c r="M56" s="33"/>
+      <c r="L56" s="29"/>
+      <c r="M56" s="28"/>
       <c r="O56" s="12"/>
-      <c r="AA56" s="34"/>
+      <c r="AA56" s="29"/>
     </row>
     <row r="57" spans="1:27">
-      <c r="A57" s="33"/>
+      <c r="A57" s="28"/>
       <c r="C57" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="L57" s="34"/>
-      <c r="M57" s="33"/>
+      <c r="L57" s="29"/>
+      <c r="M57" s="28"/>
       <c r="O57" s="14" t="s">
-        <v>272</v>
-      </c>
-      <c r="AA57" s="34"/>
+        <v>233</v>
+      </c>
+      <c r="AA57" s="29"/>
     </row>
     <row r="58" spans="1:27">
-      <c r="A58" s="33"/>
+      <c r="A58" s="28"/>
       <c r="D58" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="L58" s="34"/>
-      <c r="M58" s="33"/>
-      <c r="AA58" s="34"/>
+      <c r="L58" s="29"/>
+      <c r="M58" s="28"/>
+      <c r="AA58" s="29"/>
     </row>
     <row r="59" spans="1:27">
-      <c r="A59" s="33"/>
+      <c r="A59" s="28"/>
       <c r="D59" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="L59" s="34"/>
-      <c r="M59" s="33"/>
-      <c r="AA59" s="34"/>
+      <c r="L59" s="29"/>
+      <c r="M59" s="28"/>
+      <c r="AA59" s="29"/>
     </row>
     <row r="60" spans="1:27">
-      <c r="A60" s="33"/>
+      <c r="A60" s="28"/>
       <c r="C60" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="L60" s="34"/>
-      <c r="M60" s="33"/>
-      <c r="AA60" s="34"/>
+      <c r="L60" s="29"/>
+      <c r="M60" s="28"/>
+      <c r="AA60" s="29"/>
     </row>
     <row r="61" spans="1:27">
-      <c r="A61" s="35"/>
-      <c r="B61" s="36"/>
-      <c r="C61" s="36"/>
-      <c r="D61" s="36"/>
-      <c r="E61" s="36"/>
-      <c r="F61" s="36"/>
-      <c r="G61" s="36"/>
-      <c r="H61" s="36"/>
-      <c r="I61" s="36"/>
-      <c r="J61" s="36"/>
-      <c r="K61" s="36"/>
-      <c r="L61" s="37"/>
-      <c r="M61" s="35"/>
-      <c r="N61" s="36"/>
-      <c r="O61" s="36"/>
-      <c r="P61" s="36"/>
-      <c r="Q61" s="36"/>
-      <c r="R61" s="36"/>
-      <c r="S61" s="36"/>
-      <c r="T61" s="36"/>
-      <c r="U61" s="36"/>
-      <c r="V61" s="36"/>
-      <c r="W61" s="36"/>
-      <c r="X61" s="36"/>
-      <c r="Y61" s="36"/>
-      <c r="Z61" s="36"/>
-      <c r="AA61" s="37"/>
-    </row>
-    <row r="62" spans="1:27">
-      <c r="A62" s="18" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="63" spans="1:27">
-      <c r="B63" s="19" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="64" spans="1:27">
-      <c r="B64" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="C64" s="15"/>
-    </row>
-    <row r="65" spans="2:4">
-      <c r="B65" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C65" s="15"/>
-    </row>
-    <row r="66" spans="2:4">
-      <c r="B66" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C66" s="15"/>
-    </row>
-    <row r="67" spans="2:4">
-      <c r="B67" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="68" spans="2:4">
-      <c r="B68" s="19" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="69" spans="2:4">
-      <c r="B69" s="10" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="70" spans="2:4">
-      <c r="B70" s="10" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="71" spans="2:4">
-      <c r="B71" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="D71" s="14" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="72" spans="2:4">
-      <c r="B72" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="C72" s="16"/>
-    </row>
-    <row r="73" spans="2:4">
-      <c r="B73" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="C73" s="16"/>
-    </row>
-    <row r="74" spans="2:4" ht="17.399999999999999">
-      <c r="B74" s="13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="75" spans="2:4">
-      <c r="B75" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="76" spans="2:4">
-      <c r="C76" s="14" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="77" spans="2:4">
-      <c r="C77" s="14" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="78" spans="2:4">
-      <c r="C78" s="14" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="79" spans="2:4">
-      <c r="C79" s="14" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="80" spans="2:4">
-      <c r="C80" s="14" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="81" spans="2:3">
-      <c r="C81" s="12"/>
-    </row>
-    <row r="82" spans="2:3">
-      <c r="C82" s="14" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="83" spans="2:3">
-      <c r="C83" s="14" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="84" spans="2:3">
-      <c r="C84" s="14" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="85" spans="2:3">
-      <c r="C85" s="14" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="86" spans="2:3">
-      <c r="C86" s="14" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="87" spans="2:3">
-      <c r="C87" s="14" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="88" spans="2:3">
-      <c r="C88" s="14" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="89" spans="2:3">
-      <c r="C89" s="14" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="90" spans="2:3">
-      <c r="C90" s="14" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="91" spans="2:3">
-      <c r="C91" s="12"/>
-    </row>
-    <row r="92" spans="2:3">
-      <c r="C92" s="14" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="93" spans="2:3">
-      <c r="C93" s="14" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="95" spans="2:3" ht="17.399999999999999">
-      <c r="B95" s="13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="96" spans="2:3">
-      <c r="B96" s="19" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="97" spans="2:3">
-      <c r="B97" s="3" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="98" spans="2:3">
-      <c r="B98" s="3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="99" spans="2:3">
-      <c r="B99" s="19" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="100" spans="2:3">
-      <c r="B100" s="3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="101" spans="2:3">
-      <c r="B101" s="10" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="102" spans="2:3">
-      <c r="C102" s="14" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="103" spans="2:3">
-      <c r="B103" s="3" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="104" spans="2:3" ht="17.399999999999999">
-      <c r="B104" s="13" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="105" spans="2:3">
-      <c r="B105" s="19" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="106" spans="2:3">
-      <c r="B106" s="19" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="107" spans="2:3">
-      <c r="B107" s="19" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="108" spans="2:3">
-      <c r="B108" s="19" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="109" spans="2:3">
-      <c r="B109" s="19" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="110" spans="2:3" ht="12" customHeight="1"/>
-    <row r="111" spans="2:3" ht="12" customHeight="1"/>
-    <row r="112" spans="2:3" ht="12" customHeight="1"/>
+      <c r="A61" s="30"/>
+      <c r="B61" s="31"/>
+      <c r="C61" s="31"/>
+      <c r="D61" s="31"/>
+      <c r="E61" s="31"/>
+      <c r="F61" s="31"/>
+      <c r="G61" s="31"/>
+      <c r="H61" s="31"/>
+      <c r="I61" s="31"/>
+      <c r="J61" s="31"/>
+      <c r="K61" s="31"/>
+      <c r="L61" s="32"/>
+      <c r="M61" s="30"/>
+      <c r="N61" s="31"/>
+      <c r="O61" s="31"/>
+      <c r="P61" s="31"/>
+      <c r="Q61" s="31"/>
+      <c r="R61" s="31"/>
+      <c r="S61" s="31"/>
+      <c r="T61" s="31"/>
+      <c r="U61" s="31"/>
+      <c r="V61" s="31"/>
+      <c r="W61" s="31"/>
+      <c r="X61" s="31"/>
+      <c r="Y61" s="31"/>
+      <c r="Z61" s="31"/>
+      <c r="AA61" s="32"/>
+    </row>
+    <row r="110" ht="12" customHeight="1"/>
+    <row r="111" ht="12" customHeight="1"/>
+    <row r="112" ht="12" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:Y77"/>
+  <dimension ref="A1:Y76"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <sheetData>
     <row r="1" spans="1:25" ht="33" customHeight="1">
       <c r="A1" s="7" t="s">
-        <v>286</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:25" ht="22.8">
       <c r="B2" s="4" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" ht="22.8">
-      <c r="B4" t="s">
-        <v>288</v>
-      </c>
-      <c r="T4" s="4" t="s">
-        <v>328</v>
+        <v>248</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" ht="22.8">
+      <c r="B3" t="s">
+        <v>249</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
+      <c r="B4" s="1" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="5" spans="1:25">
       <c r="B5" s="1" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25">
-      <c r="B6" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="T5" s="15" t="s">
         <v>290</v>
       </c>
-      <c r="T6" s="17" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" ht="17.399999999999999">
-      <c r="B7" s="21" t="s">
+    </row>
+    <row r="6" spans="1:25" ht="17.399999999999999">
+      <c r="B6" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="T6" s="18" t="s">
         <v>291</v>
       </c>
-      <c r="T7" s="23" t="s">
-        <v>330</v>
+    </row>
+    <row r="7" spans="1:25">
+      <c r="B7" s="16" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="8" spans="1:25">
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="T8" s="36" t="s">
         <v>292</v>
       </c>
+      <c r="U8" s="36"/>
+      <c r="V8" s="36" t="s">
+        <v>293</v>
+      </c>
+      <c r="W8" s="36"/>
+      <c r="X8" s="36"/>
+      <c r="Y8" s="36"/>
     </row>
     <row r="9" spans="1:25">
-      <c r="B9" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="T9" s="40" t="s">
-        <v>331</v>
-      </c>
-      <c r="U9" s="40"/>
-      <c r="V9" s="40" t="s">
-        <v>332</v>
-      </c>
-      <c r="W9" s="40"/>
-      <c r="X9" s="40"/>
-      <c r="Y9" s="40"/>
+      <c r="B9" s="3"/>
+      <c r="T9" s="35" t="s">
+        <v>294</v>
+      </c>
+      <c r="U9" s="35"/>
+      <c r="V9" s="37" t="s">
+        <v>295</v>
+      </c>
+      <c r="W9" s="37"/>
+      <c r="X9" s="37"/>
+      <c r="Y9" s="37"/>
     </row>
     <row r="10" spans="1:25">
-      <c r="B10" s="3"/>
-      <c r="T10" s="38" t="s">
-        <v>333</v>
-      </c>
-      <c r="U10" s="38"/>
-      <c r="V10" s="39" t="s">
-        <v>334</v>
-      </c>
-      <c r="W10" s="39"/>
-      <c r="X10" s="39"/>
-      <c r="Y10" s="39"/>
+      <c r="B10" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="T10" s="35" t="s">
+        <v>296</v>
+      </c>
+      <c r="U10" s="35"/>
+      <c r="V10" s="37" t="s">
+        <v>297</v>
+      </c>
+      <c r="W10" s="37"/>
+      <c r="X10" s="37"/>
+      <c r="Y10" s="37"/>
     </row>
     <row r="11" spans="1:25">
-      <c r="B11" s="22" t="s">
-        <v>320</v>
-      </c>
-      <c r="T11" s="38" t="s">
-        <v>335</v>
-      </c>
-      <c r="U11" s="38"/>
-      <c r="V11" s="39" t="s">
-        <v>336</v>
-      </c>
-      <c r="W11" s="39"/>
-      <c r="X11" s="39"/>
-      <c r="Y11" s="39"/>
+      <c r="B11" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="T11" s="35" t="s">
+        <v>298</v>
+      </c>
+      <c r="U11" s="35"/>
+      <c r="V11" s="37" t="s">
+        <v>299</v>
+      </c>
+      <c r="W11" s="37"/>
+      <c r="X11" s="37"/>
+      <c r="Y11" s="37"/>
     </row>
     <row r="12" spans="1:25">
-      <c r="B12" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="T12" s="38" t="s">
-        <v>337</v>
-      </c>
-      <c r="U12" s="38"/>
-      <c r="V12" s="39" t="s">
-        <v>338</v>
-      </c>
-      <c r="W12" s="39"/>
-      <c r="X12" s="39"/>
-      <c r="Y12" s="39"/>
+      <c r="B12" s="3"/>
+      <c r="T12" s="35" t="s">
+        <v>300</v>
+      </c>
+      <c r="U12" s="35"/>
+      <c r="V12" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="W12" s="37"/>
+      <c r="X12" s="37"/>
+      <c r="Y12" s="37"/>
     </row>
     <row r="13" spans="1:25">
-      <c r="B13" s="3"/>
-      <c r="T13" s="38" t="s">
-        <v>339</v>
-      </c>
-      <c r="U13" s="38"/>
-      <c r="V13" s="39" t="s">
-        <v>340</v>
-      </c>
-      <c r="W13" s="39"/>
-      <c r="X13" s="39"/>
-      <c r="Y13" s="39"/>
-    </row>
-    <row r="14" spans="1:25">
-      <c r="B14" t="s">
-        <v>321</v>
-      </c>
-      <c r="T14" s="38" t="s">
-        <v>341</v>
-      </c>
-      <c r="U14" s="38"/>
-      <c r="V14" s="39" t="s">
-        <v>342</v>
-      </c>
-      <c r="W14" s="39"/>
-      <c r="X14" s="39"/>
-      <c r="Y14" s="39"/>
-    </row>
-    <row r="15" spans="1:25" ht="22.8">
-      <c r="B15" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="T15" s="38" t="s">
-        <v>343</v>
-      </c>
-      <c r="U15" s="38"/>
-      <c r="V15" s="39" t="s">
-        <v>344</v>
-      </c>
-      <c r="W15" s="39"/>
-      <c r="X15" s="39"/>
-      <c r="Y15" s="39"/>
-    </row>
-    <row r="16" spans="1:25" ht="17.399999999999999">
-      <c r="C16" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="T16" s="38" t="s">
-        <v>345</v>
-      </c>
-      <c r="U16" s="38"/>
-      <c r="V16" s="39" t="s">
-        <v>346</v>
-      </c>
-      <c r="W16" s="39"/>
-      <c r="X16" s="39"/>
-      <c r="Y16" s="39"/>
-    </row>
-    <row r="17" spans="2:25">
-      <c r="C17" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="T17" s="38" t="s">
-        <v>347</v>
-      </c>
-      <c r="U17" s="38"/>
-      <c r="V17" s="39" t="s">
-        <v>348</v>
-      </c>
-      <c r="W17" s="39"/>
-      <c r="X17" s="39"/>
-      <c r="Y17" s="39"/>
-    </row>
-    <row r="18" spans="2:25" ht="17.399999999999999">
-      <c r="C18" s="13" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="19" spans="2:25">
-      <c r="C19" s="1" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="20" spans="2:25">
-      <c r="C20" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="21" spans="2:25" ht="22.8">
-      <c r="B21" s="4" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="22" spans="2:25">
-      <c r="B22" s="12"/>
-    </row>
-    <row r="23" spans="2:25">
+      <c r="B13" t="s">
+        <v>282</v>
+      </c>
+      <c r="T13" s="35" t="s">
+        <v>302</v>
+      </c>
+      <c r="U13" s="35"/>
+      <c r="V13" s="37" t="s">
+        <v>303</v>
+      </c>
+      <c r="W13" s="37"/>
+      <c r="X13" s="37"/>
+      <c r="Y13" s="37"/>
+    </row>
+    <row r="14" spans="1:25" ht="22.8">
+      <c r="B14" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="T14" s="35" t="s">
+        <v>304</v>
+      </c>
+      <c r="U14" s="35"/>
+      <c r="V14" s="37" t="s">
+        <v>305</v>
+      </c>
+      <c r="W14" s="37"/>
+      <c r="X14" s="37"/>
+      <c r="Y14" s="37"/>
+    </row>
+    <row r="15" spans="1:25" ht="17.399999999999999">
+      <c r="C15" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="T15" s="35" t="s">
+        <v>306</v>
+      </c>
+      <c r="U15" s="35"/>
+      <c r="V15" s="37" t="s">
+        <v>307</v>
+      </c>
+      <c r="W15" s="37"/>
+      <c r="X15" s="37"/>
+      <c r="Y15" s="37"/>
+    </row>
+    <row r="16" spans="1:25">
+      <c r="C16" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="T16" s="35" t="s">
+        <v>308</v>
+      </c>
+      <c r="U16" s="35"/>
+      <c r="V16" s="37" t="s">
+        <v>309</v>
+      </c>
+      <c r="W16" s="37"/>
+      <c r="X16" s="37"/>
+      <c r="Y16" s="37"/>
+    </row>
+    <row r="17" spans="2:3" ht="17.399999999999999">
+      <c r="C17" s="13" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="C18" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="C19" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" ht="22.8">
+      <c r="B20" s="4" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21" s="12"/>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22" s="14"/>
+    </row>
+    <row r="23" spans="2:3">
       <c r="B23" s="14"/>
     </row>
-    <row r="24" spans="2:25">
+    <row r="24" spans="2:3">
       <c r="B24" s="14"/>
     </row>
-    <row r="25" spans="2:25">
+    <row r="25" spans="2:3">
       <c r="B25" s="14"/>
     </row>
-    <row r="26" spans="2:25">
+    <row r="26" spans="2:3">
       <c r="B26" s="14"/>
     </row>
-    <row r="27" spans="2:25">
+    <row r="27" spans="2:3">
       <c r="B27" s="14"/>
     </row>
-    <row r="28" spans="2:25">
+    <row r="28" spans="2:3">
       <c r="B28" s="14"/>
     </row>
-    <row r="29" spans="2:25">
+    <row r="29" spans="2:3">
       <c r="B29" s="14"/>
     </row>
-    <row r="30" spans="2:25">
+    <row r="30" spans="2:3">
       <c r="B30" s="14"/>
     </row>
-    <row r="31" spans="2:25">
-      <c r="B31" s="14"/>
-    </row>
-    <row r="33" spans="2:2" ht="17.399999999999999">
-      <c r="B33" s="13"/>
+    <row r="32" spans="2:3" ht="17.399999999999999">
+      <c r="B32" s="13"/>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="12"/>
     </row>
     <row r="34" spans="2:2">
-      <c r="B34" s="12"/>
+      <c r="B34" s="14"/>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" s="14"/>
@@ -11014,14 +9833,14 @@
     <row r="36" spans="2:2">
       <c r="B36" s="14"/>
     </row>
-    <row r="37" spans="2:2">
-      <c r="B37" s="14"/>
+    <row r="39" spans="2:2">
+      <c r="B39" s="1"/>
     </row>
     <row r="40" spans="2:2">
-      <c r="B40" s="1"/>
+      <c r="B40" s="11"/>
     </row>
     <row r="41" spans="2:2">
-      <c r="B41" s="11"/>
+      <c r="B41" s="1"/>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" s="1"/>
@@ -11032,246 +9851,243 @@
     <row r="44" spans="2:2">
       <c r="B44" s="1"/>
     </row>
-    <row r="45" spans="2:2">
-      <c r="B45" s="1"/>
-    </row>
-    <row r="49" spans="2:21" ht="22.8">
-      <c r="B49" s="4" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="50" spans="2:21" ht="22.8">
-      <c r="T50" s="4" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="51" spans="2:21" ht="17.399999999999999">
-      <c r="C51" s="13" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="52" spans="2:21">
+    <row r="48" spans="2:2" ht="22.8">
+      <c r="B48" s="4" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" ht="22.8">
+      <c r="T49" s="4" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" ht="17.399999999999999">
+      <c r="C50" s="13" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21">
+      <c r="C51" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="T51" s="15" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21">
       <c r="C52" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="T52" s="17" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="53" spans="2:21">
-      <c r="C53" s="1" t="s">
-        <v>298</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="T52" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21">
+      <c r="C53" s="12"/>
+      <c r="D53" s="14"/>
       <c r="T53" s="1" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="54" spans="2:21">
-      <c r="C54" s="12"/>
-      <c r="D54" s="14"/>
+        <v>313</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21">
+      <c r="D54" s="14" t="s">
+        <v>260</v>
+      </c>
       <c r="T54" s="1" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="55" spans="2:21">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" ht="22.8">
       <c r="D55" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="T55" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="56" spans="2:21" ht="22.8">
+        <v>261</v>
+      </c>
+      <c r="T55" s="4" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="56" spans="3:21">
       <c r="D56" s="14" t="s">
-        <v>300</v>
-      </c>
-      <c r="T56" s="4" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="57" spans="2:21">
+        <v>262</v>
+      </c>
+      <c r="T56" s="14" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="57" spans="3:21">
       <c r="D57" s="14" t="s">
-        <v>301</v>
-      </c>
-      <c r="T57" s="14" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="58" spans="2:21">
-      <c r="D58" s="14" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="59" spans="2:21">
-      <c r="D59" s="14"/>
-      <c r="T59" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="60" spans="2:21" ht="17.399999999999999">
-      <c r="C60" s="13" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="61" spans="2:21" ht="27.6">
-      <c r="C61" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="T61" s="24" t="s">
-        <v>372</v>
-      </c>
-      <c r="U61" s="24" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21">
+      <c r="D58" s="14"/>
+      <c r="T58" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" ht="17.399999999999999">
+      <c r="C59" s="13" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" ht="27.6">
+      <c r="C60" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="T60" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="U60" s="19" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" ht="41.4">
+      <c r="D61" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="T61" s="22">
+        <v>0</v>
+      </c>
+      <c r="U61" s="20" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" ht="55.2">
+      <c r="D62" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="T62" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="U62" s="20" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" ht="27.6">
+      <c r="D63" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="T63" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="U63" s="20" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" ht="22.8">
+      <c r="D64" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="T64" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="65" spans="3:21">
+      <c r="T65" s="11" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="66" spans="3:21" ht="17.399999999999999">
+      <c r="C66" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="T66" s="1" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="62" spans="2:21" ht="41.4">
-      <c r="D62" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="T62" s="27">
-        <v>0</v>
-      </c>
-      <c r="U62" s="25" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="63" spans="2:21" ht="55.2">
-      <c r="D63" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="T63" s="28" t="s">
-        <v>357</v>
-      </c>
-      <c r="U63" s="25" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="64" spans="2:21" ht="27.6">
-      <c r="D64" s="14" t="s">
-        <v>306</v>
-      </c>
-      <c r="T64" s="28" t="s">
-        <v>359</v>
-      </c>
-      <c r="U64" s="25" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="65" spans="3:21" ht="22.8">
-      <c r="D65" s="14" t="s">
-        <v>307</v>
-      </c>
-      <c r="T65" s="4" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="66" spans="3:21">
-      <c r="T66" s="11" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="67" spans="3:21" ht="17.399999999999999">
-      <c r="C67" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="T67" s="1" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="68" spans="3:21">
-      <c r="C68" s="1" t="s">
-        <v>309</v>
+    <row r="67" spans="3:21">
+      <c r="C67" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="68" spans="3:21" ht="17.399999999999999">
+      <c r="D68" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="T68" s="21" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="69" spans="3:21" ht="17.399999999999999">
-      <c r="D69" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="T69" s="26" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="70" spans="3:21" ht="17.399999999999999">
+      <c r="D69" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="U69" s="13" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="70" spans="3:21">
       <c r="D70" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="U70" s="13" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="71" spans="3:21">
+        <v>273</v>
+      </c>
+      <c r="U70" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="71" spans="3:21" ht="17.399999999999999">
       <c r="D71" s="14" t="s">
-        <v>312</v>
-      </c>
-      <c r="U71" t="s">
-        <v>363</v>
+        <v>274</v>
+      </c>
+      <c r="U71" s="13" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="72" spans="3:21" ht="17.399999999999999">
-      <c r="D72" s="14" t="s">
-        <v>313</v>
-      </c>
-      <c r="U72" s="13" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="73" spans="3:21" ht="17.399999999999999">
-      <c r="C73" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="U73" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="74" spans="3:21">
+      <c r="C72" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="U72" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="73" spans="3:21">
+      <c r="C73" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="U73" s="14" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="74" spans="3:21" ht="17.399999999999999">
       <c r="C74" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="U74" s="14" t="s">
-        <v>366</v>
+        <v>277</v>
+      </c>
+      <c r="U74" s="13" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="75" spans="3:21" ht="17.399999999999999">
-      <c r="C75" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="U75" s="13" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="76" spans="3:21" ht="17.399999999999999">
-      <c r="C76" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="U76" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="77" spans="3:21">
-      <c r="C77" s="1" t="s">
-        <v>318</v>
+      <c r="C75" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="U75" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="76" spans="3:21">
+      <c r="C76" s="1" t="s">
+        <v>279</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="V14:Y14"/>
+    <mergeCell ref="V15:Y15"/>
+    <mergeCell ref="V16:Y16"/>
+    <mergeCell ref="T13:U13"/>
     <mergeCell ref="T14:U14"/>
-    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="V8:Y8"/>
     <mergeCell ref="V9:Y9"/>
     <mergeCell ref="V10:Y10"/>
     <mergeCell ref="V11:Y11"/>
     <mergeCell ref="V12:Y12"/>
     <mergeCell ref="V13:Y13"/>
-    <mergeCell ref="V14:Y14"/>
+    <mergeCell ref="T8:U8"/>
     <mergeCell ref="T9:U9"/>
     <mergeCell ref="T10:U10"/>
     <mergeCell ref="T11:U11"/>
     <mergeCell ref="T12:U12"/>
-    <mergeCell ref="T13:U13"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="V15:Y15"/>
-    <mergeCell ref="V16:Y16"/>
-    <mergeCell ref="V17:Y17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -11285,57 +10101,57 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30">
       <c r="A1" s="7" t="s">
-        <v>374</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="22.8">
       <c r="B2" s="4" t="s">
-        <v>375</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="B3" s="5" t="s">
-        <v>376</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="14.4">
       <c r="B4" s="1" t="s">
-        <v>377</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="B5" s="1" t="s">
-        <v>378</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="1" t="s">
-        <v>379</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="22.8">
       <c r="B7" s="4" t="s">
-        <v>380</v>
+        <v>341</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" s="1" t="s">
-        <v>381</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="B9" s="3" t="s">
-        <v>382</v>
+        <v>343</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="B10" s="3" t="s">
-        <v>383</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="14.4">
       <c r="B11" s="1" t="s">
-        <v>384</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -11345,137 +10161,137 @@
     </row>
     <row r="13" spans="1:4" ht="22.8">
       <c r="D13" s="4" t="s">
-        <v>385</v>
+        <v>346</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="17.399999999999999">
       <c r="D14" s="13" t="s">
-        <v>386</v>
+        <v>347</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="D15" s="14" t="s">
-        <v>387</v>
+        <v>348</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="22.8">
       <c r="D16" s="4" t="s">
-        <v>388</v>
+        <v>349</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="17.399999999999999">
       <c r="D17" s="13" t="s">
-        <v>389</v>
+        <v>350</v>
       </c>
     </row>
     <row r="18" spans="2:4">
       <c r="D18" s="1" t="s">
-        <v>390</v>
+        <v>351</v>
       </c>
     </row>
     <row r="19" spans="2:4">
       <c r="D19" s="1" t="s">
-        <v>391</v>
+        <v>352</v>
       </c>
     </row>
     <row r="20" spans="2:4">
       <c r="D20" s="1" t="s">
-        <v>392</v>
+        <v>353</v>
       </c>
     </row>
     <row r="21" spans="2:4">
       <c r="D21" s="1" t="s">
-        <v>393</v>
+        <v>354</v>
       </c>
     </row>
     <row r="22" spans="2:4" ht="17.399999999999999">
       <c r="D22" s="13" t="s">
-        <v>394</v>
+        <v>355</v>
       </c>
     </row>
     <row r="23" spans="2:4">
       <c r="D23" s="1" t="s">
-        <v>395</v>
+        <v>356</v>
       </c>
     </row>
     <row r="24" spans="2:4">
       <c r="D24" s="1" t="s">
-        <v>396</v>
+        <v>357</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="17.399999999999999">
       <c r="D25" s="13" t="s">
-        <v>397</v>
+        <v>358</v>
       </c>
     </row>
     <row r="26" spans="2:4">
       <c r="D26" s="1" t="s">
-        <v>398</v>
+        <v>359</v>
       </c>
     </row>
     <row r="27" spans="2:4">
       <c r="D27" s="1" t="s">
-        <v>399</v>
+        <v>360</v>
       </c>
     </row>
     <row r="28" spans="2:4">
       <c r="D28" s="1" t="s">
-        <v>400</v>
+        <v>361</v>
       </c>
     </row>
     <row r="29" spans="2:4" ht="22.8">
       <c r="D29" s="4" t="s">
-        <v>401</v>
+        <v>362</v>
       </c>
     </row>
     <row r="30" spans="2:4">
       <c r="D30" t="s">
-        <v>402</v>
+        <v>363</v>
       </c>
     </row>
     <row r="31" spans="2:4" ht="22.8">
       <c r="B31" s="4" t="s">
-        <v>403</v>
+        <v>364</v>
       </c>
     </row>
     <row r="32" spans="2:4">
       <c r="B32" t="s">
-        <v>404</v>
+        <v>365</v>
       </c>
     </row>
     <row r="33" spans="2:10" ht="17.399999999999999">
       <c r="B33" s="13" t="s">
-        <v>405</v>
+        <v>366</v>
       </c>
     </row>
     <row r="34" spans="2:10">
       <c r="B34" s="1" t="s">
-        <v>406</v>
+        <v>367</v>
       </c>
     </row>
     <row r="35" spans="2:10">
       <c r="B35" s="1" t="s">
-        <v>407</v>
+        <v>368</v>
       </c>
     </row>
     <row r="36" spans="2:10">
       <c r="B36" s="1" t="s">
-        <v>408</v>
+        <v>369</v>
       </c>
     </row>
     <row r="37" spans="2:10" ht="17.399999999999999">
       <c r="B37" s="13" t="s">
-        <v>409</v>
+        <v>370</v>
       </c>
     </row>
     <row r="38" spans="2:10">
       <c r="B38" s="1" t="s">
-        <v>410</v>
+        <v>371</v>
       </c>
     </row>
     <row r="39" spans="2:10">
       <c r="B39" s="2" t="s">
-        <v>411</v>
+        <v>372</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
@@ -11487,8 +10303,8 @@
       <c r="J39" s="5"/>
     </row>
     <row r="40" spans="2:10">
-      <c r="B40" s="21" t="s">
-        <v>461</v>
+      <c r="B40" s="16" t="s">
+        <v>422</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
@@ -11500,8 +10316,8 @@
       <c r="J40" s="5"/>
     </row>
     <row r="41" spans="2:10">
-      <c r="B41" s="21" t="s">
-        <v>412</v>
+      <c r="B41" s="16" t="s">
+        <v>373</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
@@ -11514,202 +10330,202 @@
     </row>
     <row r="43" spans="2:10" ht="22.8">
       <c r="B43" s="4" t="s">
-        <v>413</v>
+        <v>374</v>
       </c>
     </row>
     <row r="44" spans="2:10">
       <c r="C44" s="14" t="s">
-        <v>414</v>
+        <v>375</v>
       </c>
     </row>
     <row r="45" spans="2:10" ht="17.399999999999999">
       <c r="C45" s="13" t="s">
-        <v>415</v>
+        <v>376</v>
       </c>
     </row>
     <row r="46" spans="2:10">
       <c r="C46" s="1" t="s">
-        <v>416</v>
+        <v>377</v>
       </c>
     </row>
     <row r="47" spans="2:10">
       <c r="C47" s="1" t="s">
-        <v>417</v>
+        <v>378</v>
       </c>
     </row>
     <row r="48" spans="2:10">
       <c r="C48" s="1" t="s">
-        <v>418</v>
+        <v>379</v>
       </c>
     </row>
     <row r="49" spans="3:5">
       <c r="C49" s="3" t="s">
-        <v>419</v>
+        <v>380</v>
       </c>
     </row>
     <row r="50" spans="3:5">
       <c r="C50" s="3" t="s">
-        <v>420</v>
+        <v>381</v>
       </c>
     </row>
     <row r="51" spans="3:5">
       <c r="C51" s="3" t="s">
-        <v>421</v>
+        <v>382</v>
       </c>
     </row>
     <row r="52" spans="3:5">
       <c r="C52" s="3" t="s">
-        <v>422</v>
+        <v>383</v>
       </c>
     </row>
     <row r="53" spans="3:5" ht="22.8">
       <c r="C53" s="4" t="s">
-        <v>423</v>
+        <v>384</v>
       </c>
     </row>
     <row r="54" spans="3:5">
       <c r="C54" s="2" t="s">
-        <v>424</v>
+        <v>385</v>
       </c>
     </row>
     <row r="55" spans="3:5">
       <c r="C55" s="2" t="s">
-        <v>425</v>
+        <v>386</v>
       </c>
     </row>
     <row r="56" spans="3:5">
       <c r="C56" s="1" t="s">
-        <v>426</v>
+        <v>387</v>
       </c>
     </row>
     <row r="57" spans="3:5" ht="17.399999999999999">
       <c r="E57" s="13" t="s">
-        <v>258</v>
+        <v>219</v>
       </c>
     </row>
     <row r="58" spans="3:5">
       <c r="E58" s="14" t="s">
-        <v>427</v>
+        <v>388</v>
       </c>
     </row>
     <row r="59" spans="3:5">
       <c r="E59" s="14" t="s">
-        <v>428</v>
+        <v>389</v>
       </c>
     </row>
     <row r="60" spans="3:5">
       <c r="E60" s="14" t="s">
-        <v>429</v>
+        <v>390</v>
       </c>
     </row>
     <row r="61" spans="3:5">
       <c r="E61" s="14" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
     </row>
     <row r="62" spans="3:5">
       <c r="E62" s="14" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
     </row>
     <row r="63" spans="3:5">
       <c r="E63" s="14" t="s">
-        <v>430</v>
+        <v>391</v>
       </c>
     </row>
     <row r="64" spans="3:5">
       <c r="E64" s="14" t="s">
-        <v>431</v>
+        <v>392</v>
       </c>
     </row>
     <row r="65" spans="5:5">
       <c r="E65" s="14" t="s">
-        <v>432</v>
+        <v>393</v>
       </c>
     </row>
     <row r="66" spans="5:5">
       <c r="E66" s="14" t="s">
-        <v>433</v>
+        <v>394</v>
       </c>
     </row>
     <row r="67" spans="5:5">
       <c r="E67" s="14" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
     </row>
     <row r="68" spans="5:5">
       <c r="E68" s="14" t="s">
-        <v>434</v>
+        <v>395</v>
       </c>
     </row>
     <row r="69" spans="5:5">
       <c r="E69" s="14" t="s">
-        <v>435</v>
+        <v>396</v>
       </c>
     </row>
     <row r="70" spans="5:5">
       <c r="E70" s="14" t="s">
-        <v>436</v>
+        <v>397</v>
       </c>
     </row>
     <row r="71" spans="5:5">
       <c r="E71" s="14" t="s">
-        <v>437</v>
+        <v>398</v>
       </c>
     </row>
     <row r="72" spans="5:5">
       <c r="E72" s="14" t="s">
-        <v>433</v>
+        <v>394</v>
       </c>
     </row>
     <row r="73" spans="5:5">
       <c r="E73" s="14" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
     </row>
     <row r="74" spans="5:5">
       <c r="E74" s="14" t="s">
-        <v>438</v>
+        <v>399</v>
       </c>
     </row>
     <row r="75" spans="5:5">
       <c r="E75" s="14" t="s">
-        <v>439</v>
+        <v>400</v>
       </c>
     </row>
     <row r="76" spans="5:5">
       <c r="E76" s="14" t="s">
-        <v>440</v>
+        <v>401</v>
       </c>
     </row>
     <row r="77" spans="5:5">
       <c r="E77" s="14" t="s">
-        <v>441</v>
+        <v>402</v>
       </c>
     </row>
     <row r="78" spans="5:5">
       <c r="E78" s="14" t="s">
-        <v>442</v>
+        <v>403</v>
       </c>
     </row>
     <row r="79" spans="5:5">
       <c r="E79" s="14" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
     </row>
     <row r="80" spans="5:5">
       <c r="E80" s="14" t="s">
-        <v>443</v>
+        <v>404</v>
       </c>
     </row>
     <row r="81" spans="2:10">
       <c r="E81" s="14" t="s">
-        <v>444</v>
+        <v>405</v>
       </c>
     </row>
     <row r="82" spans="2:10">
       <c r="E82" s="14" t="s">
-        <v>230</v>
+        <v>205</v>
       </c>
     </row>
     <row r="83" spans="2:10">
@@ -11719,111 +10535,111 @@
     </row>
     <row r="84" spans="2:10" ht="22.8">
       <c r="C84" s="4" t="s">
-        <v>445</v>
+        <v>406</v>
       </c>
     </row>
     <row r="86" spans="2:10">
-      <c r="B86" s="40" t="s">
-        <v>446</v>
-      </c>
-      <c r="C86" s="40"/>
-      <c r="D86" s="40" t="s">
-        <v>447</v>
-      </c>
-      <c r="E86" s="40"/>
-      <c r="F86" s="40"/>
-      <c r="G86" s="40"/>
-      <c r="H86" s="40" t="s">
-        <v>448</v>
-      </c>
-      <c r="I86" s="40"/>
-      <c r="J86" s="40"/>
+      <c r="B86" s="36" t="s">
+        <v>407</v>
+      </c>
+      <c r="C86" s="36"/>
+      <c r="D86" s="36" t="s">
+        <v>408</v>
+      </c>
+      <c r="E86" s="36"/>
+      <c r="F86" s="36"/>
+      <c r="G86" s="36"/>
+      <c r="H86" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="I86" s="36"/>
+      <c r="J86" s="36"/>
     </row>
     <row r="87" spans="2:10">
-      <c r="B87" s="42" t="s">
-        <v>449</v>
-      </c>
-      <c r="C87" s="43"/>
-      <c r="D87" s="41" t="s">
-        <v>450</v>
-      </c>
-      <c r="E87" s="41"/>
-      <c r="F87" s="41"/>
-      <c r="G87" s="41"/>
-      <c r="H87" s="41" t="s">
-        <v>451</v>
-      </c>
-      <c r="I87" s="41"/>
-      <c r="J87" s="41"/>
+      <c r="B87" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="C87" s="40"/>
+      <c r="D87" s="38" t="s">
+        <v>411</v>
+      </c>
+      <c r="E87" s="38"/>
+      <c r="F87" s="38"/>
+      <c r="G87" s="38"/>
+      <c r="H87" s="38" t="s">
+        <v>412</v>
+      </c>
+      <c r="I87" s="38"/>
+      <c r="J87" s="38"/>
     </row>
     <row r="88" spans="2:10">
-      <c r="B88" s="42" t="s">
-        <v>452</v>
-      </c>
-      <c r="C88" s="43"/>
-      <c r="D88" s="41" t="s">
-        <v>453</v>
-      </c>
-      <c r="E88" s="41"/>
-      <c r="F88" s="41"/>
-      <c r="G88" s="41"/>
-      <c r="H88" s="41" t="s">
-        <v>454</v>
-      </c>
-      <c r="I88" s="41"/>
-      <c r="J88" s="41"/>
+      <c r="B88" s="39" t="s">
+        <v>413</v>
+      </c>
+      <c r="C88" s="40"/>
+      <c r="D88" s="38" t="s">
+        <v>414</v>
+      </c>
+      <c r="E88" s="38"/>
+      <c r="F88" s="38"/>
+      <c r="G88" s="38"/>
+      <c r="H88" s="38" t="s">
+        <v>415</v>
+      </c>
+      <c r="I88" s="38"/>
+      <c r="J88" s="38"/>
     </row>
     <row r="89" spans="2:10">
-      <c r="B89" s="41" t="s">
-        <v>455</v>
-      </c>
-      <c r="C89" s="41"/>
-      <c r="D89" s="41" t="s">
-        <v>456</v>
-      </c>
-      <c r="E89" s="41"/>
-      <c r="F89" s="41"/>
-      <c r="G89" s="41"/>
-      <c r="H89" s="41" t="s">
-        <v>457</v>
-      </c>
-      <c r="I89" s="41"/>
-      <c r="J89" s="41"/>
+      <c r="B89" s="38" t="s">
+        <v>416</v>
+      </c>
+      <c r="C89" s="38"/>
+      <c r="D89" s="38" t="s">
+        <v>417</v>
+      </c>
+      <c r="E89" s="38"/>
+      <c r="F89" s="38"/>
+      <c r="G89" s="38"/>
+      <c r="H89" s="38" t="s">
+        <v>418</v>
+      </c>
+      <c r="I89" s="38"/>
+      <c r="J89" s="38"/>
     </row>
     <row r="90" spans="2:10">
-      <c r="B90" s="41" t="s">
-        <v>458</v>
-      </c>
-      <c r="C90" s="41"/>
-      <c r="D90" s="41" t="s">
-        <v>459</v>
-      </c>
-      <c r="E90" s="41"/>
-      <c r="F90" s="41"/>
-      <c r="G90" s="41"/>
-      <c r="H90" s="41" t="s">
-        <v>460</v>
-      </c>
-      <c r="I90" s="41"/>
-      <c r="J90" s="41"/>
+      <c r="B90" s="38" t="s">
+        <v>419</v>
+      </c>
+      <c r="C90" s="38"/>
+      <c r="D90" s="38" t="s">
+        <v>420</v>
+      </c>
+      <c r="E90" s="38"/>
+      <c r="F90" s="38"/>
+      <c r="G90" s="38"/>
+      <c r="H90" s="38" t="s">
+        <v>421</v>
+      </c>
+      <c r="I90" s="38"/>
+      <c r="J90" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="H86:J86"/>
+    <mergeCell ref="H87:J87"/>
+    <mergeCell ref="H88:J88"/>
+    <mergeCell ref="H89:J89"/>
+    <mergeCell ref="H90:J90"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
     <mergeCell ref="D86:G86"/>
     <mergeCell ref="D87:G87"/>
     <mergeCell ref="D88:G88"/>
     <mergeCell ref="D89:G89"/>
     <mergeCell ref="D90:G90"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="H86:J86"/>
-    <mergeCell ref="H87:J87"/>
-    <mergeCell ref="H88:J88"/>
-    <mergeCell ref="H89:J89"/>
-    <mergeCell ref="H90:J90"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
